--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI59"/>
+  <dimension ref="A1:BI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46108.875</v>
+        <v>46108.89583333334</v>
       </c>
     </row>
     <row r="57">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,203 +11968,6 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46108.89583333334</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI59" s="3" t="n">
         <v>46108.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI58"/>
+  <dimension ref="A1:BI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>4.35</v>
+        <v>5.71</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
         <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>1.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>5.15</v>
       </c>
       <c r="R27" t="n">
-        <v>3.65</v>
+        <v>8.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46108.875</v>
+        <v>46108.89583333334</v>
       </c>
     </row>
     <row r="56">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,203 +11771,6 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46108.89583333334</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI58" s="3" t="n">
         <v>46108.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>5.71</v>
+        <v>4.35</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R26" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>5.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R18" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>5.71</v>
+        <v>3.95</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,17 +4146,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>3.95</v>
+        <v>5.71</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R25" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>1.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>5.15</v>
       </c>
       <c r="R27" t="n">
-        <v>3.65</v>
+        <v>8.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>5.71</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="R24" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>8.5</v>
+        <v>2.58</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>3.95</v>
+        <v>4.54</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R27" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>4.37</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>5.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>5.71</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.37</v>
+        <v>3.95</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>3.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R23" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R25" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.75</v>
+        <v>5.71</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.35</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>5.71</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>5.15</v>
       </c>
       <c r="R24" t="n">
-        <v>3.65</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>5.71</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>3.95</v>
+        <v>4.54</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>4.54</v>
+        <v>5.71</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R26" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R15" t="n">
-        <v>3.95</v>
+        <v>4.37</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.35</v>
+        <v>2.75</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>4.54</v>
+        <v>5.71</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>5.71</v>
+        <v>4.54</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R26" t="n">
-        <v>2.96</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.37</v>
+        <v>3.95</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>4.37</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R24" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>8.5</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.37</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.75</v>
+        <v>4.54</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R20" t="n">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.15</v>
+        <v>3.18</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>2.96</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>4.35</v>
+        <v>5.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R18" t="n">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>5.71</v>
+        <v>4.54</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.37</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.15</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>8.5</v>
+        <v>3.41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R27" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>4.35</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>4.54</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>5.71</v>
+        <v>4.35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.54</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R25" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,10 +11281,10 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11478,10 +11478,10 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>4.35</v>
+        <v>5.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R25" t="n">
-        <v>2.96</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R27" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>5.71</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>4.35</v>
+        <v>4.54</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>5.71</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
         <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.54</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R23" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
         <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>5.71</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>4.37</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
         <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.35</v>
+        <v>3.95</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>3.41</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>8.5</v>
+        <v>2.58</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R25" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R26" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>3.15</v>
+        <v>4.54</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD55" t="n">
         <v>2.15</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R56" t="n">
-        <v>4.54</v>
+        <v>3.15</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD56" t="n">
         <v>2.15</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>5.71</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.54</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,17 +4146,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R25" t="n">
-        <v>2.96</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R26" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R55" t="n">
-        <v>4.54</v>
+        <v>3.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD55" t="n">
         <v>2.15</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>3.15</v>
+        <v>4.54</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD56" t="n">
         <v>2.15</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2774,130 +2774,130 @@
         <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD13" t="n">
         <v>3.3</v>
       </c>
-      <c r="R13" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>5.71</v>
+        <v>2.71</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD16" t="n">
         <v>3.3</v>
       </c>
-      <c r="R16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>4.37</v>
+        <v>4.82</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.54</v>
+        <v>3.95</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,80 +4347,80 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R26" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5735,124 +5735,124 @@
         <v>4.6</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>3.15</v>
+        <v>4.54</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD55" t="n">
         <v>2.15</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R56" t="n">
-        <v>4.54</v>
+        <v>3.15</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD56" t="n">
         <v>2.15</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,28 +2968,28 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R13" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X13" t="n">
         <v>3</v>
@@ -2998,49 +2998,49 @@
         <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AE13" t="n">
         <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,67 +3165,67 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
         <v>1.85</v>
@@ -3234,10 +3234,10 @@
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,67 +3559,67 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
         <v>3.4</v>
       </c>
-      <c r="R16" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.28</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="X16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
         <v>1.85</v>
@@ -3628,64 +3628,64 @@
         <v>1.85</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC16" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>2.94</v>
       </c>
       <c r="R17" t="n">
-        <v>4.82</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>5.25</v>
+        <v>3.59</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI17" t="n">
         <v>8</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BD17" t="n">
         <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,67 +3953,67 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD18" t="n">
         <v>3.3</v>
       </c>
-      <c r="R18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3</v>
-      </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK18" t="n">
         <v>1.85</v>
@@ -4025,7 +4025,7 @@
         <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>6.51</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3.59</v>
+        <v>6.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
         <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,61 +4347,61 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>6.51</v>
+        <v>4.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>6.83</v>
+        <v>5.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
         <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
         <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
@@ -4410,16 +4410,16 @@
         <v>1.07</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
         <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>8.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R23" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>8.5</v>
+        <v>2.58</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R55" t="n">
-        <v>4.54</v>
+        <v>3.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD55" t="n">
         <v>2.15</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>3.15</v>
+        <v>4.54</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD56" t="n">
         <v>2.15</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
         <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
         <v>1.3</v>
       </c>
       <c r="AN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD13" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="R14" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5</v>
+        <v>3.59</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="X14" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.59</v>
+        <v>4.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD17" t="n">
         <v>3</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AE17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>4.78</v>
+        <v>6.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>5.28</v>
+        <v>6.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="X18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="BC18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>6.51</v>
+        <v>2.71</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="U19" t="n">
-        <v>6.83</v>
+        <v>3.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC19" t="n">
         <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,28 +4347,28 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="S20" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -4377,49 +4377,49 @@
         <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AE20" t="n">
         <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.07</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.18</v>
+        <v>5.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.96</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>3.04</v>
+        <v>1.76</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>3.84</v>
+        <v>7.65</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
         <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.98</v>
+        <v>2.88</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AN23" t="n">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BD23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R24" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="R25" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>3.41</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R27" t="n">
         <v>3.4</v>
       </c>
-      <c r="R27" t="n">
-        <v>4.6</v>
-      </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>5.38</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
         <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH27" t="n">
         <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
         <v>1.29</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE27" t="n">
         <v>1.57</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK55" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11448,124 +11448,124 @@
         <v>4.54</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AY56" t="n">
         <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11645,70 +11645,70 @@
         <v>4.05</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
-        <v>4.78</v>
+        <v>2.75</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>5.28</v>
+        <v>3.59</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="X13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AE13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AL13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD13" t="n">
         <v>3.2</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>4.82</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>3.59</v>
+        <v>5.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="X14" t="n">
         <v>3</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AN14" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BD14" t="n">
         <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
         <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>4.5</v>
+        <v>5.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.42</v>
@@ -3780,7 +3780,7 @@
         <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
         <v>1.33</v>
@@ -3789,10 +3789,10 @@
         <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
         <v>1.33</v>
@@ -3804,7 +3804,7 @@
         <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
         <v>3.6</v>
@@ -3813,22 +3813,22 @@
         <v>1.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>6.51</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
-        <v>6.83</v>
+        <v>3.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
         <v>1.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.71</v>
+        <v>6.51</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3.4</v>
+        <v>6.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
         <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
         <v>1.3</v>
       </c>
       <c r="AN20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>5.38</v>
+        <v>3.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X22" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
         <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>2.17</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.05</v>
+        <v>8.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL22" t="n">
         <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="S23" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>7.65</v>
+        <v>5.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.45</v>
+        <v>6.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AL23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL24" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AM24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="R25" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>3.8</v>
+        <v>7.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
         <v>2.62</v>
@@ -5362,103 +5362,103 @@
         <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.95</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
         <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3.3</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5729,76 +5729,76 @@
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S27" t="n">
         <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.42</v>
       </c>
-      <c r="W27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z27" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
         <v>1.04</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI27" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>3</v>
+        <v>4.54</v>
       </c>
       <c r="S55" t="n">
-        <v>3.39</v>
+        <v>2.9</v>
       </c>
       <c r="T55" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="U55" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="V55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC55" t="n">
         <v>1.7</v>
-      </c>
-      <c r="W55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.65</v>
       </c>
       <c r="AD55" t="n">
         <v>2.1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="AF55" t="n">
         <v>1.33</v>
       </c>
       <c r="AG55" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI55" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AJ55" t="n">
         <v>1</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AS55" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AX55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>2</v>
-      </c>
       <c r="BA55" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R56" t="n">
-        <v>4.54</v>
+        <v>3</v>
       </c>
       <c r="S56" t="n">
-        <v>2.9</v>
+        <v>3.39</v>
       </c>
       <c r="T56" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="U56" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="V56" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W56" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="X56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD56" t="n">
         <v>2.1</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AF56" t="n">
         <v>1.33</v>
       </c>
       <c r="AG56" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI56" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AJ56" t="n">
         <v>1</v>
       </c>
       <c r="AK56" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE56" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF56" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI57"/>
+  <dimension ref="A1:BI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46108.5</v>
+        <v>46108.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46108.58333333334</v>
+        <v>46108.5</v>
       </c>
     </row>
     <row r="5">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46108.625</v>
+        <v>46108.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.46</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.75</v>
+        <v>5.21</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.59</v>
+        <v>5.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>2.41</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.7</v>
+        <v>3.96</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>1.53</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46108.64583333334</v>
+        <v>46108.625</v>
       </c>
     </row>
     <row r="14">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,130 +3559,130 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC16" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
         <v>1.11</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AM17" t="n">
         <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
         <v>1.13</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,130 +3953,130 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>4.82</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="T18" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z18" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC18" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF18" t="n">
         <v>1.12</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
         <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>6.51</v>
+        <v>6.2</v>
       </c>
       <c r="S19" t="n">
         <v>2.08</v>
@@ -4168,49 +4168,49 @@
         <v>6.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
         <v>2.59</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
         <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
         <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
         <v>2.2</v>
@@ -4267,7 +4267,7 @@
         <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BD19" t="n">
         <v>3.3</v>
@@ -4276,7 +4276,7 @@
         <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,76 +4347,76 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R20" t="n">
-        <v>4.78</v>
+        <v>4.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>5.28</v>
+        <v>4.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
         <v>1.13</v>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>4.5</v>
+        <v>3.54</v>
       </c>
       <c r="V21" t="n">
         <v>1.48</v>
@@ -4568,55 +4568,55 @@
         <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,16 +4658,16 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
         <v>1.12</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46108.66666666666</v>
+        <v>46108.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>3.84</v>
+        <v>5.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA22" t="n">
         <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46108.69791666666</v>
+        <v>46108.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>5.38</v>
+        <v>3.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.62</v>
       </c>
-      <c r="X23" t="n">
-        <v>2.78</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
         <v>3.08</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>1.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1</v>
+        <v>7.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
         <v>2.62</v>
@@ -5165,103 +5165,103 @@
         <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
         <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN24" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>9</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="BC25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5532,76 +5532,76 @@
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S26" t="n">
         <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.42</v>
       </c>
-      <c r="W26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z26" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
         <v>1.04</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI26" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AL27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD27" t="n">
         <v>3</v>
       </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE27" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46108.75</v>
+        <v>46108.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46108.875</v>
+        <v>46108.75</v>
       </c>
     </row>
     <row r="30">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46108.875</v>
+        <v>46108.89583333334</v>
       </c>
     </row>
     <row r="49">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46108.875</v>
+        <v>46108.89583333334</v>
       </c>
     </row>
     <row r="50">
@@ -10204,27 +10204,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,19 +10371,19 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10392,1385 +10392,6 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46108.875</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Stepojevac Vaga</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Tekstilac Odžaci</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" s="3" t="n">
-        <v>46108.875</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>FAP</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI52" s="3" t="n">
-        <v>46108.875</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI53" s="3" t="n">
-        <v>46108.875</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Estudiantes Caseros</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Central Norte</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="3" t="n">
-        <v>46108.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>San Martín San Juan</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U55" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="3" t="n">
-        <v>46108.89583333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Chaco For Ever</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="3" t="n">
-        <v>46108.89583333334</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="3" t="n">
         <v>46108.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="R15" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>4.66</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,80 +3559,80 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.94</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE16" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AL16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>4.73</v>
+        <v>2.78</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>5.28</v>
+        <v>3.54</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AL17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>4.82</v>
+        <v>6.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>4.3</v>
+        <v>6.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -3983,49 +3983,49 @@
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="U20" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="V20" t="n">
         <v>1.42</v>
@@ -4371,55 +4371,55 @@
         <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AD20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG20" t="n">
         <v>3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
         <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.78</v>
+        <v>4.73</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>3.54</v>
+        <v>5.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
         <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.04</v>
+        <v>3.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>1.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>3.1</v>
+        <v>7.65</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>2.62</v>
@@ -4968,103 +4968,103 @@
         <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
         <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN23" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL23" t="n">
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2</v>
       </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD23" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>7.65</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
         <v>2.62</v>
@@ -5165,103 +5165,103 @@
         <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AA24" t="n">
         <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.6</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W25" t="n">
         <v>2.62</v>
       </c>
       <c r="X25" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
         <v>7.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH25" t="n">
         <v>1.26</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB25" t="n">
         <v>1.29</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
         <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AL26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3</v>
       </c>
-      <c r="AH26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD27" t="n">
         <v>3</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AE27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AN27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X28" t="n">
         <v>2.62</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.78</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
         <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R48" t="n">
-        <v>4.54</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.9</v>
+        <v>3.39</v>
       </c>
       <c r="T48" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="U48" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W48" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="X48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD48" t="n">
         <v>2.1</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AF48" t="n">
         <v>1.33</v>
       </c>
       <c r="AG48" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI48" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AJ48" t="n">
         <v>1</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AM48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE48" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN48" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF48" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3</v>
+        <v>4.54</v>
       </c>
       <c r="S49" t="n">
-        <v>3.39</v>
+        <v>2.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="U49" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="V49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC49" t="n">
         <v>1.7</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X49" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
         <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="AF49" t="n">
         <v>1.33</v>
       </c>
       <c r="AG49" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI49" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AJ49" t="n">
         <v>1</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AX49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2</v>
-      </c>
       <c r="BA49" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BD49" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
         <v>2.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.82</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U16" t="n">
-        <v>4.3</v>
+        <v>4.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="X16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG16" t="n">
         <v>3</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,16 +3676,16 @@
         <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD16" t="n">
         <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="R17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>6.2</v>
+        <v>4.82</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>6.83</v>
+        <v>4.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -3983,49 +3983,49 @@
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="R20" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="V20" t="n">
         <v>1.42</v>
@@ -4371,55 +4371,55 @@
         <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
         <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>4.73</v>
+        <v>2.78</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>5.28</v>
+        <v>3.54</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
         <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AL21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>3.15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.76</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>7.65</v>
+        <v>3.55</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X23" t="n">
         <v>2.62</v>
@@ -4968,103 +4968,103 @@
         <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>4.73</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>8.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
         <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN24" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.62</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.78</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
         <v>7.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG25" t="n">
         <v>3.08</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.04</v>
+        <v>2.22</v>
       </c>
       <c r="T26" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
-        <v>3.84</v>
+        <v>4.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X26" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AL26" t="n">
         <v>1.8</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.41</v>
+        <v>1.57</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.76</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.85</v>
+        <v>3.78</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="BD26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AL27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="BC27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD27" t="n">
         <v>3</v>
       </c>
-      <c r="AE27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="S28" t="n">
         <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X28" t="n">
         <v>2.9</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
         <v>1.04</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC28" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,130 +9863,130 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>4.54</v>
       </c>
       <c r="S48" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="T48" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="U48" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="V48" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="W48" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="X48" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z48" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AG48" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI48" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AJ48" t="n">
         <v>1</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AX48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2</v>
-      </c>
       <c r="BA48" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF48" t="n">
         <v>1.05</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="R49" t="n">
-        <v>4.54</v>
+        <v>3.29</v>
       </c>
       <c r="S49" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="U49" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W49" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="X49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB49" t="n">
         <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
         <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE49" t="n">
         <v>1.33</v>
       </c>
-      <c r="AG49" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF49" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10266,13 +10266,13 @@
         <v>4.05</v>
       </c>
       <c r="S50" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="T50" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V50" t="n">
         <v>1.38</v>
@@ -10284,13 +10284,13 @@
         <v>2.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
         <v>6.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB50" t="n">
         <v>1.03</v>
@@ -10302,28 +10302,28 @@
         <v>3.2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI50" t="n">
         <v>6.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM50" t="n">
         <v>1.29</v>
@@ -10374,7 +10374,7 @@
         <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BD50" t="n">
         <v>3.6</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.73</v>
+        <v>3.95</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>5.28</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
         <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3759,16 +3759,16 @@
         <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>3.6</v>
@@ -3804,22 +3804,22 @@
         <v>2.23</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
         <v>4.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.01</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
         <v>1.8</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>4.82</v>
+        <v>4.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB18" t="n">
         <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,16 +4070,16 @@
         <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" t="n">
         <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q19" t="n">
         <v>3.8</v>
@@ -4159,19 +4159,19 @@
         <v>6.2</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
         <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>6.83</v>
+        <v>5.5</v>
       </c>
       <c r="V19" t="n">
         <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -4186,40 +4186,40 @@
         <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD19" t="n">
         <v>3.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AL19" t="n">
         <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AN19" t="n">
         <v>2.5</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,58 +4347,58 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="X20" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AH20" t="n">
         <v>1.28</v>
@@ -4410,10 +4410,10 @@
         <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
         <v>1.29</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="S21" t="n">
         <v>3.1</v>
@@ -4559,7 +4559,7 @@
         <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="V21" t="n">
         <v>1.48</v>
@@ -4583,28 +4583,28 @@
         <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
         <v>3.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
         <v>4.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
         <v>1.85</v>
@@ -4658,16 +4658,16 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
         <v>2.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF21" t="n">
         <v>1.12</v>
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.9</v>
+        <v>4.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="V22" t="n">
         <v>1.48</v>
@@ -4765,13 +4765,13 @@
         <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
         <v>1.05</v>
@@ -4789,7 +4789,7 @@
         <v>1.93</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
         <v>3.25</v>
@@ -4804,10 +4804,10 @@
         <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM22" t="n">
         <v>1.3</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC22" t="n">
         <v>2.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="BE22" t="n">
         <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="U23" t="n">
-        <v>3.55</v>
+        <v>3.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="X23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
         <v>1.35</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>8.31</v>
+        <v>4.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>6.75</v>
+        <v>4.26</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="S26" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
         <v>2.62</v>
       </c>
       <c r="X26" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI26" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AJ26" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AK26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BD26" t="n">
         <v>3.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R27" t="n">
         <v>3.15</v>
       </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X27" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AM27" t="n">
         <v>1.35</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG28" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI28" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R48" t="n">
         <v>3.1</v>
       </c>
-      <c r="R48" t="n">
-        <v>4.54</v>
-      </c>
       <c r="S48" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG48" t="n">
         <v>5.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY48" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ48" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3.29</v>
+        <v>4.54</v>
       </c>
       <c r="S49" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T49" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="U49" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>2.1</v>
       </c>
-      <c r="X49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="AR49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX49" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2</v>
-      </c>
       <c r="BA49" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
         <v>2.15</v>
@@ -2983,25 +2983,25 @@
         <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
         <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
@@ -3010,13 +3010,13 @@
         <v>1.21</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
         <v>2.8</v>
@@ -3034,13 +3034,13 @@
         <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,28 +3049,28 @@
         <v>1.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU13" t="n">
         <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AY13" t="n">
         <v>1.3</v>
@@ -3082,19 +3082,19 @@
         <v>4.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,28 +3165,28 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>4.82</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>5.25</v>
+        <v>3.52</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
         <v>3</v>
@@ -3195,49 +3195,49 @@
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA14" t="n">
         <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
         <v>1.12</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R15" t="n">
-        <v>3.95</v>
+        <v>4.82</v>
       </c>
       <c r="S15" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,16 +3479,16 @@
         <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
         <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="X17" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T18" t="n">
         <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
         <v>1.42</v>
@@ -3977,55 +3977,55 @@
         <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,83 +4343,83 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,49 +4544,49 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>2.1</v>
@@ -4595,28 +4595,28 @@
         <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4938,19 +4938,19 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.04</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>3.84</v>
@@ -4965,16 +4965,16 @@
         <v>3.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AA23" t="n">
         <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC23" t="n">
         <v>1.42</v>
@@ -5001,10 +5001,10 @@
         <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AM23" t="n">
         <v>1.35</v>
@@ -5025,13 +5025,13 @@
         <v>2.41</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AV23" t="n">
         <v>2.11</v>
@@ -5040,10 +5040,10 @@
         <v>1.68</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.74</v>
@@ -5055,7 +5055,7 @@
         <v>1.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BD23" t="n">
         <v>3</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
         <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.62</v>
       </c>
-      <c r="X24" t="n">
-        <v>2.78</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
         <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG24" t="n">
         <v>3.08</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.9</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="V26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.42</v>
       </c>
-      <c r="W26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z26" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
         <v>1.04</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.35</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q27" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN27" t="n">
         <v>3.3</v>
       </c>
-      <c r="R27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
+      <c r="BF27" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.73</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>8.31</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>6.75</v>
+        <v>4.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X28" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK28" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.1</v>
+        <v>4.54</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T48" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>2.1</v>
       </c>
-      <c r="X48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="AR48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX48" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2</v>
-      </c>
       <c r="BA48" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q49" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R49" t="n">
         <v>3.1</v>
       </c>
-      <c r="R49" t="n">
-        <v>4.54</v>
-      </c>
       <c r="S49" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="W49" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="X49" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG49" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY49" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ49" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,28 +3165,28 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>6.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>3.52</v>
+        <v>5.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
         <v>3</v>
@@ -3195,49 +3195,49 @@
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,80 +3559,80 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN16" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>3.6</v>
       </c>
-      <c r="R17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,28 +4150,28 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>5.5</v>
+        <v>3.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -4180,49 +4180,49 @@
         <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,73 +4544,73 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
         <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
         <v>1.29</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
         <v>3.3</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV24" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AW24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S25" t="n">
         <v>3.2</v>
       </c>
-      <c r="R25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC25" t="n">
         <v>2.1</v>
       </c>
-      <c r="U25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q26" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
         <v>3.3</v>
       </c>
-      <c r="R26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
+      <c r="BF26" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="R27" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U27" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AI27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="AG28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2</v>
-      </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BD28" t="n">
         <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R48" t="n">
         <v>3.1</v>
       </c>
-      <c r="R48" t="n">
-        <v>4.54</v>
-      </c>
       <c r="S48" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="W48" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="X48" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG48" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY48" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ48" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>4.54</v>
       </c>
       <c r="S49" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T49" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="U49" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>2.1</v>
       </c>
-      <c r="X49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="AR49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX49" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2</v>
-      </c>
       <c r="BA49" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2983,7 +2983,7 @@
         <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
@@ -2992,7 +2992,7 @@
         <v>3.2</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
         <v>1.5</v>
@@ -3013,16 +3013,16 @@
         <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
         <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
         <v>5.25</v>
@@ -3046,40 +3046,40 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AT13" t="n">
         <v>3.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.26</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
         <v>1.18</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="S14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN14" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC14" t="n">
         <v>2.2</v>
       </c>
-      <c r="U14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>4.82</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
         <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
         <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
         <v>1.42</v>
@@ -3583,55 +3583,55 @@
         <v>2.62</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
         <v>1.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
         <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="V18" t="n">
         <v>1.42</v>
@@ -3977,55 +3977,55 @@
         <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI18" t="n">
         <v>7</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AJ18" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,83 +4343,83 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2.3</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD23" t="n">
         <v>3</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z23" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="BC23" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="BD23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.55</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>4.73</v>
       </c>
       <c r="R24" t="n">
-        <v>4.2</v>
+        <v>8.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6</v>
+        <v>6.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,19 +5332,19 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
         <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
         <v>3.1</v>
@@ -5368,7 +5368,7 @@
         <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
         <v>1.29</v>
@@ -5383,7 +5383,7 @@
         <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH25" t="n">
         <v>1.3</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="BC26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3</v>
       </c>
-      <c r="X26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5729,10 +5729,10 @@
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="S27" t="n">
         <v>2.7</v>
@@ -5741,13 +5741,13 @@
         <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="V27" t="n">
         <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="X27" t="n">
         <v>2.62</v>
@@ -5765,13 +5765,13 @@
         <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
@@ -5795,7 +5795,7 @@
         <v>2.05</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
         <v>1.65</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD28" t="n">
         <v>3.2</v>
       </c>
-      <c r="R28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV28" t="n">
         <v>2.62</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AW28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.35</v>
       </c>
-      <c r="AD28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
         <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.1</v>
+        <v>4.54</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T48" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>2.1</v>
       </c>
-      <c r="X48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="AR48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX48" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2</v>
-      </c>
       <c r="BA48" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="R49" t="n">
-        <v>4.54</v>
+        <v>3.31</v>
       </c>
       <c r="S49" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="W49" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="X49" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG49" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY49" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ49" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>4.05</v>
       </c>
       <c r="S50" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="T50" t="n">
         <v>2.15</v>
@@ -10320,10 +10320,10 @@
         <v>1.09</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM50" t="n">
         <v>1.29</v>
@@ -10374,7 +10374,7 @@
         <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BD50" t="n">
         <v>3.6</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1198,10 +1198,10 @@
         <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S4" t="n">
         <v>4.08</v>
@@ -1240,7 +1240,7 @@
         <v>2.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="AF4" t="n">
         <v>1.43</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,67 +3165,67 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
         <v>1.85</v>
@@ -3234,64 +3234,64 @@
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R15" t="n">
         <v>2.9</v>
@@ -3380,7 +3380,7 @@
         <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
         <v>2.4</v>
@@ -3419,7 +3419,7 @@
         <v>1.24</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.01</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,67 +3559,67 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH16" t="n">
         <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
         <v>1.85</v>
@@ -3628,10 +3628,10 @@
         <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,28 +4347,28 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R20" t="n">
-        <v>2.75</v>
+        <v>6.23</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>3.52</v>
+        <v>5.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -4377,49 +4377,49 @@
         <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="V21" t="n">
         <v>1.42</v>
@@ -4568,7 +4568,7 @@
         <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
@@ -4580,25 +4580,25 @@
         <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4607,16 +4607,16 @@
         <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
         <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF21" t="n">
         <v>1.13</v>
@@ -4744,13 +4744,13 @@
         <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
@@ -4765,7 +4765,7 @@
         <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
         <v>1.33</v>
@@ -4789,7 +4789,7 @@
         <v>1.93</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG22" t="n">
         <v>3.25</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R23" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="V23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.42</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z23" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>8.31</v>
+        <v>2.45</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
         <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.45</v>
+        <v>4.12</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
         <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV25" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AW25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC25" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q26" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="X26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="BD26" t="n">
         <v>4</v>
       </c>
-      <c r="AH26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U27" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
         <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AD27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD27" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE27" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U28" t="n">
         <v>3.6</v>
       </c>
-      <c r="R28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="V28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.38</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AY28" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>6.23</v>
       </c>
       <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>4.82</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
         <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,43 +4150,43 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
         <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
         <v>1.33</v>
@@ -4198,31 +4198,31 @@
         <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.74</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>6.23</v>
+        <v>2.9</v>
       </c>
       <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U20" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
         <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM21" t="n">
         <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,16 +4661,16 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
         <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.32</v>
+        <v>4.73</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1</v>
+        <v>8.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="U23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD23" t="n">
         <v>3.5</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
+      <c r="BF23" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="R24" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="X24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.48</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>8.31</v>
+        <v>2.45</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL28" t="n">
         <v>2.05</v>
       </c>
-      <c r="U28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM28" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,28 +3559,28 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>6.23</v>
+        <v>2.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
         <v>3</v>
@@ -3589,49 +3589,49 @@
         <v>1.33</v>
       </c>
       <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI16" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AJ16" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,67 +3756,67 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
         <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
         <v>1.85</v>
@@ -3825,64 +3825,64 @@
         <v>1.85</v>
       </c>
       <c r="AM17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,43 +3953,43 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
         <v>1.33</v>
@@ -4001,31 +4001,31 @@
         <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
         <v>2.4</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
         <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.82</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
         <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>8.31</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
         <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="S24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.8</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV24" t="n">
         <v>2.62</v>
       </c>
-      <c r="AE24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AW24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="AM25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX25" t="n">
         <v>1.38</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AY25" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R26" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="X26" t="n">
         <v>2.62</v>
@@ -5559,40 +5559,40 @@
         <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
         <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL26" t="n">
         <v>2.05</v>
@@ -5601,7 +5601,7 @@
         <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,13 +5643,13 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
         <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE26" t="n">
         <v>1.65</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>4.73</v>
       </c>
       <c r="R27" t="n">
-        <v>3.7</v>
+        <v>8.31</v>
       </c>
       <c r="S27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.6</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
         <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD28" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>6.23</v>
+        <v>4.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="V15" t="n">
         <v>1.42</v>
@@ -3386,7 +3386,7 @@
         <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
@@ -3398,25 +3398,25 @@
         <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
         <v>7</v>
@@ -3425,16 +3425,16 @@
         <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
         <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
         <v>1.13</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,67 +3756,67 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="n">
         <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
         <v>1.85</v>
@@ -3825,10 +3825,10 @@
         <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
         <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
         <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM18" t="n">
         <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,16 +4070,16 @@
         <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
         <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>3.74</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9</v>
+        <v>6.23</v>
       </c>
       <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD19" t="n">
         <v>3.1</v>
       </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.82</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG20" t="n">
         <v>3</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.58</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
         <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>1.03</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
         <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="X23" t="n">
         <v>2.62</v>
@@ -4968,40 +4968,40 @@
         <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL23" t="n">
         <v>2.05</v>
@@ -5010,7 +5010,7 @@
         <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,13 +5052,13 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
         <v>2.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE23" t="n">
         <v>1.65</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>4.12</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK24" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
         <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.32</v>
+        <v>4.73</v>
       </c>
       <c r="R26" t="n">
-        <v>3.1</v>
+        <v>8.31</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="U26" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3.5</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
+      <c r="BF26" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>8.31</v>
+        <v>4.12</v>
       </c>
       <c r="S27" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>6.75</v>
+        <v>4.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AN27" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BC27" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BD27" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.2</v>
       </c>
-      <c r="R28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="V28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.42</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
         <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL28" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10060,19 +10060,19 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R49" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="S49" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T49" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="U49" t="n">
         <v>4.2</v>
@@ -10129,7 +10129,7 @@
         <v>1.51</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AN49" t="n">
         <v>1.55</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="X4" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>1.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AE4" t="n">
         <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI4" t="n">
         <v>11</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2971,10 +2971,10 @@
         <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="S13" t="n">
         <v>2.15</v>
@@ -3025,10 +3025,10 @@
         <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
         <v>1.73</v>
@@ -3055,7 +3055,7 @@
         <v>2.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
         <v>3.05</v>
@@ -3073,7 +3073,7 @@
         <v>1.53</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.26</v>
@@ -3085,13 +3085,13 @@
         <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
         <v>4.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BF13" t="n">
         <v>1.24</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,67 +3165,67 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG14" t="n">
         <v>3</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.88</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
         <v>1.85</v>
@@ -3234,10 +3234,10 @@
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>4.4</v>
+        <v>6.23</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="V15" t="n">
         <v>1.42</v>
@@ -3386,7 +3386,7 @@
         <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
@@ -3398,25 +3398,25 @@
         <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" t="n">
         <v>7</v>
@@ -3425,16 +3425,16 @@
         <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
         <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
         <v>1.13</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,83 +3555,83 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,73 +3756,73 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM17" t="n">
         <v>1.29</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.49</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>6.23</v>
+        <v>2.81</v>
       </c>
       <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U19" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,67 +4347,67 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R20" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH20" t="n">
         <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
         <v>1.85</v>
@@ -4416,10 +4416,10 @@
         <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.95</v>
+        <v>3.47</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
         <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,16 +4741,16 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
@@ -4777,7 +4777,7 @@
         <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
         <v>1.29</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>4.73</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>8.31</v>
       </c>
       <c r="S24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.6</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.8</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X25" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AD25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV25" t="n">
         <v>2.62</v>
       </c>
-      <c r="AE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AW25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.31</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.73</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>8.31</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1.85</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.33</v>
       </c>
-      <c r="W26" t="n">
-        <v>3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.55</v>
       </c>
-      <c r="AM26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="Q27" t="n">
         <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.12</v>
+        <v>2.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
         <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="BC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="R28" t="n">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE28" t="n">
         <v>1.48</v>
       </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T48" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="W48" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="X48" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG48" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY48" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ48" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>3.29</v>
+        <v>4.54</v>
       </c>
       <c r="S49" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T49" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="U49" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>2.1</v>
       </c>
-      <c r="X49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="AR49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX49" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2</v>
-      </c>
       <c r="BA49" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,67 +3165,67 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="R14" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH14" t="n">
         <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
         <v>1.85</v>
@@ -3234,10 +3234,10 @@
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="Q16" t="n">
         <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="S16" t="n">
         <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,16 +3676,16 @@
         <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
         <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
         <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
         <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BD19" t="n">
         <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="R20" t="n">
-        <v>4.75</v>
+        <v>6.23</v>
       </c>
       <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC20" t="n">
         <v>2.3</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>8.31</v>
+        <v>2.39</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN25" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2</v>
-      </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" t="n">
         <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>1.31</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>4.73</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>8.31</v>
       </c>
       <c r="S26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.6</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="R27" t="n">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="X27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.48</v>
       </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="S28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W28" t="n">
         <v>2.8</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AD28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV28" t="n">
         <v>2.62</v>
       </c>
-      <c r="AE28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AW28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE28" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,118 +9863,118 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.29</v>
+        <v>4.54</v>
       </c>
       <c r="S48" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T48" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="W48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>2.1</v>
       </c>
-      <c r="X48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="AR48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX48" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.29</v>
       </c>
-      <c r="AY48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2</v>
-      </c>
       <c r="BA48" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
         <v>1.48</v>
@@ -9989,7 +9989,7 @@
         <v>1.33</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,118 +10060,118 @@
         </is>
       </c>
       <c r="P49" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T49" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="W49" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="X49" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG49" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AX49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY49" t="n">
         <v>1.22</v>
       </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ49" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="BB49" t="n">
         <v>1.48</v>
@@ -10186,7 +10186,7 @@
         <v>1.33</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,73 +3165,73 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
         <v>4.75</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U14" t="n">
-        <v>5</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM14" t="n">
         <v>1.29</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD16" t="n">
         <v>3.1</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
         <v>3.1</v>
       </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,43 +3756,43 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
         <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
         <v>1.33</v>
@@ -3804,31 +3804,31 @@
         <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI17" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>2.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>3.85</v>
+        <v>2.81</v>
       </c>
       <c r="S18" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI18" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>6.23</v>
+        <v>3.85</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.42</v>
@@ -4371,55 +4371,55 @@
         <v>2.62</v>
       </c>
       <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG20" t="n">
         <v>3</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
         <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="R23" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1.35</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AN23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="BC23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
         <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="X24" t="n">
         <v>2.62</v>
@@ -5165,40 +5165,40 @@
         <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
         <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
         <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL24" t="n">
         <v>2.05</v>
@@ -5207,7 +5207,7 @@
         <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,13 +5249,13 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC24" t="n">
         <v>2.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
         <v>1.65</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.73</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>8.31</v>
       </c>
       <c r="S25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.6</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>8.31</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W27" t="n">
         <v>2.8</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X27" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AD27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV27" t="n">
         <v>2.62</v>
       </c>
-      <c r="AE27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AW27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2</v>
-      </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BD28" t="n">
         <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,73 +3165,73 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R14" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
         <v>1.29</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="R15" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AM15" t="n">
         <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>6.23</v>
+        <v>4.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="V16" t="n">
         <v>1.42</v>
@@ -3583,7 +3583,7 @@
         <v>2.62</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y16" t="n">
         <v>1.33</v>
@@ -3595,25 +3595,25 @@
         <v>1.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" t="n">
         <v>7</v>
@@ -3622,16 +3622,16 @@
         <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD16" t="n">
         <v>3.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
         <v>1.13</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD18" t="n">
         <v>3.1</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="AE18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG18" t="n">
         <v>3.1</v>
       </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,83 +4343,83 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>4.82</v>
+        <v>3.85</v>
       </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG21" t="n">
         <v>3</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.58</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,16 +4661,16 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
         <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="BD23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.55</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
         <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
         <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.31</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.73</v>
+        <v>2.93</v>
       </c>
       <c r="R25" t="n">
-        <v>8.31</v>
+        <v>3.22</v>
       </c>
       <c r="S25" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>6.75</v>
+        <v>3.6</v>
       </c>
       <c r="V25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.33</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD25" t="n">
         <v>3</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4</v>
-      </c>
       <c r="BE25" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,80 +5529,80 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.52</v>
+        <v>1.31</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>4.73</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>8.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="U26" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
         <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="Q27" t="n">
         <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.1</v>
+        <v>2.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
         <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="BC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R28" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="V28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.42</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
         <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL28" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -801,40 +801,40 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>4.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>5.54</v>
+        <v>5.65</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="X2" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
@@ -843,31 +843,31 @@
         <v>1.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AM2" t="n">
         <v>1.14</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,67 +3165,67 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>1.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
         <v>1.85</v>
@@ -3234,64 +3234,64 @@
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,28 +3362,28 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>4.82</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
         <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>5.25</v>
+        <v>3.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
         <v>3</v>
@@ -3398,43 +3398,43 @@
         <v>1.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF15" t="n">
         <v>1.12</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,73 +3559,73 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R16" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="X16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
         <v>1.29</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="Q17" t="n">
         <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="BD17" t="n">
         <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.53</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="R19" t="n">
-        <v>2.81</v>
+        <v>4.82</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
         <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,83 +4343,83 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="R21" t="n">
-        <v>3.85</v>
+        <v>6.23</v>
       </c>
       <c r="S21" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="V21" t="n">
         <v>1.42</v>
@@ -4568,55 +4568,55 @@
         <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI21" t="n">
         <v>7</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AJ21" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,16 +4661,16 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
         <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R24" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN24" t="n">
         <v>3.3</v>
       </c>
-      <c r="R24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG25" t="n">
         <v>3.22</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="AH25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL25" t="n">
         <v>2.05</v>
       </c>
-      <c r="U25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>8.31</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>6.75</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
         <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.39</v>
+        <v>4.1</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
         <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="X27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV27" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AW27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="R28" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.35</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AN28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="BC28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-03-27.xlsx
+++ b/jogos_2026-03-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI50"/>
+  <dimension ref="A1:BI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,43 +3362,43 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.46</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
         <v>1.33</v>
@@ -3410,31 +3410,31 @@
         <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,80 +3756,80 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.53</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>2.81</v>
+        <v>3.85</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AN17" t="n">
         <v>1.88</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,83 +3949,83 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,28 +4150,28 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
       <c r="R19" t="n">
-        <v>4.82</v>
+        <v>6.23</v>
       </c>
       <c r="S19" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -4180,49 +4180,49 @@
         <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>1.55</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,43 +4347,43 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y20" t=